--- a/output/pdf_financials_xlsx/DGS.xlsx
+++ b/output/pdf_financials_xlsx/DGS.xlsx
@@ -888,25 +888,25 @@
         <v>1.110301</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>2.447478</v>
+        <v>2.534917</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.694392</v>
+        <v>6.123149</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.319787</v>
+        <v>3.995991</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.402822</v>
+        <v>4.384813</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>3.330433</v>
+        <v>8.940206</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>3.793637</v>
+        <v>5.160919</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>3.249344</v>
+        <v>4.582252</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>3.084181</v>
@@ -937,7 +937,7 @@
         <v>-1.110301</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-2.447478</v>
+        <v>-2.534917</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0007560000000000001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000599</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003216</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.005041</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-10.863039</v>
+        <v>-10.863795</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>9.515340999999999</v>
+        <v>9.514742</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.101199</v>
+        <v>2.097983</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-6.108408</v>
@@ -1925,7 +1925,7 @@
         <v>9.584773</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>21.365705</v>
+        <v>21.360664</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -2024,13 +2024,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.863039</v>
+        <v>-10.863795</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>9.515340999999999</v>
+        <v>9.514742</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.101199</v>
+        <v>2.097983</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-6.108408</v>
@@ -2039,7 +2039,7 @@
         <v>9.584773</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>21.365705</v>
+        <v>21.360664</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -2330,31 +2330,31 @@
         <v>0</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.710212</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.166422</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.244721</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.98134</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.782575</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>9.165075</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.229059</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.462612</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>2.505449</v>
       </c>
     </row>
     <row r="35">
@@ -2428,31 +2428,31 @@
         <v>0.710212</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.320078</v>
+        <v>1.03029</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.166422</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.244721</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.98134</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>5.782575</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>9.165075</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.229059</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.462612</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>2.505449</v>
       </c>
     </row>
     <row r="37">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -54792,7 +54792,7 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -57312,7 +57312,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E605" s="5" t="n">

--- a/output/pdf_financials_xlsx/DGS.xlsx
+++ b/output/pdf_financials_xlsx/DGS.xlsx
@@ -54314,7 +54314,11 @@
           <t>Net investment income (loss) before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D568" t="inlineStr"/>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E568" t="inlineStr">
         <is>
           <t>-</t>
@@ -54386,7 +54390,11 @@
           <t>Distributions on Preferred shares (note 6)</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E569" t="inlineStr">
         <is>
           <t>-</t>
@@ -55834,7 +55842,11 @@
           <t>Distributions on Preferred shares (note 7)</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E587" s="5" t="n">
         <v>-0.811842</v>
       </c>
@@ -56816,7 +56828,11 @@
           <t>Net investment income before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D599" t="inlineStr"/>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E599" t="inlineStr">
         <is>
           <t>-</t>
